--- a/Result/profitability/1417.xlsx
+++ b/Result/profitability/1417.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.52</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03625000000000002</v>
+        <v>0.07250000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>36.935</v>
+        <v>41.92625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04375000000000002</v>
+        <v>0.11875</v>
       </c>
       <c r="N3" t="n">
-        <v>38.64875</v>
+        <v>51.24249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.09875000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>46.68624999999999</v>
+        <v>46.44875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07375000000000002</v>
+        <v>0.08125000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>43.86625</v>
+        <v>45.16875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06500000000000002</v>
+        <v>0.06000000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>41.24625</v>
+        <v>42.62125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07875000000000001</v>
+        <v>0.04000000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>40.32375</v>
+        <v>40.97375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02500000000000002</v>
+        <v>0.06875000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>37.55375</v>
+        <v>36.73375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>71</v>
+      </c>
+      <c r="D75" t="n">
+        <v>28</v>
+      </c>
+      <c r="E75" t="n">
+        <v>43</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-15.40%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>37</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.01249999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.415</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.590909090909091</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.559999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09815950920245387</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2090270812437311</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
